--- a/data/nzd0548/nzd0548.xlsx
+++ b/data/nzd0548/nzd0548.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K524"/>
+  <dimension ref="A1:K526"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20862,6 +20862,84 @@
       <c r="K524" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-10 22:26:38+00:00</t>
+        </is>
+      </c>
+      <c r="B525" t="n">
+        <v>318.48</v>
+      </c>
+      <c r="C525" t="n">
+        <v>312.1</v>
+      </c>
+      <c r="D525" t="n">
+        <v>333.04</v>
+      </c>
+      <c r="E525" t="n">
+        <v>320.73</v>
+      </c>
+      <c r="F525" t="n">
+        <v>320.07</v>
+      </c>
+      <c r="G525" t="n">
+        <v>313.56</v>
+      </c>
+      <c r="H525" t="n">
+        <v>304.79</v>
+      </c>
+      <c r="I525" t="n">
+        <v>309.49</v>
+      </c>
+      <c r="J525" t="n">
+        <v>307.48</v>
+      </c>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:32+00:00</t>
+        </is>
+      </c>
+      <c r="B526" t="n">
+        <v>317.55</v>
+      </c>
+      <c r="C526" t="n">
+        <v>311.7</v>
+      </c>
+      <c r="D526" t="n">
+        <v>332.26</v>
+      </c>
+      <c r="E526" t="n">
+        <v>320</v>
+      </c>
+      <c r="F526" t="n">
+        <v>319.41</v>
+      </c>
+      <c r="G526" t="n">
+        <v>313.15</v>
+      </c>
+      <c r="H526" t="n">
+        <v>304.61</v>
+      </c>
+      <c r="I526" t="n">
+        <v>308.9</v>
+      </c>
+      <c r="J526" t="n">
+        <v>307.13</v>
+      </c>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -20876,7 +20954,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B550"/>
+  <dimension ref="A1:B552"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26379,6 +26457,26 @@
       </c>
       <c r="B550" t="n">
         <v>0.82</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>2026-08-10 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B551" t="n">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B552" t="n">
+        <v>0.22</v>
       </c>
     </row>
   </sheetData>
@@ -26547,28 +26645,28 @@
         <v>0.0565</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3784649458187285</v>
+        <v>-0.372728107319064</v>
       </c>
       <c r="J2" t="n">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="K2" t="n">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1745635472725501</v>
+        <v>0.1705975031905989</v>
       </c>
       <c r="M2" t="n">
-        <v>4.389010648113126</v>
+        <v>4.39612536580026</v>
       </c>
       <c r="N2" t="n">
-        <v>38.37986513162467</v>
+        <v>38.45340407751156</v>
       </c>
       <c r="O2" t="n">
-        <v>6.195148515703612</v>
+        <v>6.201080879775038</v>
       </c>
       <c r="P2" t="n">
-        <v>320.6398188422372</v>
+        <v>320.5779432245232</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26625,28 +26723,28 @@
         <v>0.0852</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1396568440029891</v>
+        <v>-0.1358761632004966</v>
       </c>
       <c r="J3" t="n">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="K3" t="n">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04484390322153331</v>
+        <v>0.04273099687194082</v>
       </c>
       <c r="M3" t="n">
-        <v>3.831885076762533</v>
+        <v>3.836475997960771</v>
       </c>
       <c r="N3" t="n">
-        <v>23.69390196423515</v>
+        <v>23.69990061534928</v>
       </c>
       <c r="O3" t="n">
-        <v>4.867638232678672</v>
+        <v>4.868254370444223</v>
       </c>
       <c r="P3" t="n">
-        <v>310.6267579663809</v>
+        <v>310.586167293959</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26703,28 +26801,28 @@
         <v>0.0808</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.191650632019142</v>
+        <v>-0.1858320702842171</v>
       </c>
       <c r="J4" t="n">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="K4" t="n">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="L4" t="n">
-        <v>0.06981529277330711</v>
+        <v>0.06593474566238688</v>
       </c>
       <c r="M4" t="n">
-        <v>4.193666609763423</v>
+        <v>4.206162606480442</v>
       </c>
       <c r="N4" t="n">
-        <v>27.91131755150896</v>
+        <v>28.03323485951348</v>
       </c>
       <c r="O4" t="n">
-        <v>5.283116272760704</v>
+        <v>5.294642089840774</v>
       </c>
       <c r="P4" t="n">
-        <v>330.0607161506931</v>
+        <v>329.9982464724793</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26781,28 +26879,28 @@
         <v>0.08119999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2226475092127393</v>
+        <v>-0.21740014763641</v>
       </c>
       <c r="J5" t="n">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="K5" t="n">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="L5" t="n">
-        <v>0.089851396988335</v>
+        <v>0.08618245433033445</v>
       </c>
       <c r="M5" t="n">
-        <v>4.218038902634535</v>
+        <v>4.227824931879467</v>
       </c>
       <c r="N5" t="n">
-        <v>28.67314899231582</v>
+        <v>28.7497469354121</v>
       </c>
       <c r="O5" t="n">
-        <v>5.354731458468839</v>
+        <v>5.361879048935373</v>
       </c>
       <c r="P5" t="n">
-        <v>319.3798360918875</v>
+        <v>319.3235042244328</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26859,28 +26957,28 @@
         <v>0.0701</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1522583978827841</v>
+        <v>-0.1467906726604769</v>
       </c>
       <c r="J6" t="n">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="K6" t="n">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04661645472155418</v>
+        <v>0.04351307560977558</v>
       </c>
       <c r="M6" t="n">
-        <v>4.262832847234464</v>
+        <v>4.271368660548273</v>
       </c>
       <c r="N6" t="n">
-        <v>27.23571794507148</v>
+        <v>27.33449847396746</v>
       </c>
       <c r="O6" t="n">
-        <v>5.218785102403765</v>
+        <v>5.22824047591228</v>
       </c>
       <c r="P6" t="n">
-        <v>316.5441536383334</v>
+        <v>316.4856031883386</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26937,28 +27035,28 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00919065034331088</v>
+        <v>0.01579229346643831</v>
       </c>
       <c r="J7" t="n">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="K7" t="n">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="L7" t="n">
-        <v>6.549757858476113e-05</v>
+        <v>0.000194229463154505</v>
       </c>
       <c r="M7" t="n">
-        <v>6.778432432440571</v>
+        <v>6.77981908908506</v>
       </c>
       <c r="N7" t="n">
-        <v>73.67979058486353</v>
+        <v>73.69246558703229</v>
       </c>
       <c r="O7" t="n">
-        <v>8.583693295130221</v>
+        <v>8.584431582057853</v>
       </c>
       <c r="P7" t="n">
-        <v>304.2766866257739</v>
+        <v>304.2058531248477</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27015,28 +27113,28 @@
         <v>0.1109</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1045914171222884</v>
+        <v>0.1066883189946918</v>
       </c>
       <c r="J8" t="n">
+        <v>525</v>
+      </c>
+      <c r="K8" t="n">
         <v>523</v>
       </c>
-      <c r="K8" t="n">
-        <v>521</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.01149227930387864</v>
+        <v>0.01204606187166768</v>
       </c>
       <c r="M8" t="n">
-        <v>5.916595342277995</v>
+        <v>5.90220676309207</v>
       </c>
       <c r="N8" t="n">
-        <v>53.85753426978177</v>
+        <v>53.68131388316313</v>
       </c>
       <c r="O8" t="n">
-        <v>7.338769261244134</v>
+        <v>7.326753297550227</v>
       </c>
       <c r="P8" t="n">
-        <v>299.0631569583597</v>
+        <v>299.0406722665123</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27093,28 +27191,28 @@
         <v>0.095</v>
       </c>
       <c r="I9" t="n">
-        <v>0.07714615962543199</v>
+        <v>0.08522235822697427</v>
       </c>
       <c r="J9" t="n">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="K9" t="n">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002728529882016217</v>
+        <v>0.003344263751722809</v>
       </c>
       <c r="M9" t="n">
-        <v>9.386449375613839</v>
+        <v>9.385206541928822</v>
       </c>
       <c r="N9" t="n">
-        <v>123.2637401723911</v>
+        <v>123.2280511518891</v>
       </c>
       <c r="O9" t="n">
-        <v>11.10242046458299</v>
+        <v>11.10081308517034</v>
       </c>
       <c r="P9" t="n">
-        <v>296.3705579201239</v>
+        <v>296.2834492990166</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27171,28 +27269,28 @@
         <v>0.1205</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1540994236590629</v>
+        <v>0.1548527306108798</v>
       </c>
       <c r="J10" t="n">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="K10" t="n">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="L10" t="n">
-        <v>0.06213264943130559</v>
+        <v>0.06319255210779418</v>
       </c>
       <c r="M10" t="n">
-        <v>3.53686717028453</v>
+        <v>3.526967989189199</v>
       </c>
       <c r="N10" t="n">
-        <v>20.44394800704988</v>
+        <v>20.37000701013838</v>
       </c>
       <c r="O10" t="n">
-        <v>4.521498424974832</v>
+        <v>4.513314415165243</v>
       </c>
       <c r="P10" t="n">
-        <v>302.1247183768036</v>
+        <v>302.1166312071298</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27230,7 +27328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K524"/>
+  <dimension ref="A1:K526"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57061,6 +57159,120 @@
         </is>
       </c>
     </row>
+    <row r="525">
+      <c r="A525" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-10 22:26:38+00:00</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>-46.590789773991204,168.80590618007776</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>-46.59017579019428,168.8060276089976</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>-46.589536155605046,168.80577148688732</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>-46.58895023430081,168.8054143034778</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>-46.58841360948312,168.80492387779003</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>-46.58792198029762,168.8043355375238</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>-46.58744116180394,168.80374737238975</t>
+        </is>
+      </c>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>-46.58705641603759,168.8030156028952</t>
+        </is>
+      </c>
+      <c r="J525" t="inlineStr">
+        <is>
+          <t>-46.58666625124933,168.8023020319416</t>
+        </is>
+      </c>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:32+00:00</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>-46.59079043581677,168.80591826696823</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>-46.59017604732649,168.80603281061852</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>-46.58953453249629,168.80578137967458</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>-46.58894691855302,168.80542251591044</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>-46.588410087723176,168.80493080177766</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>-46.58791942925912,168.80433939481318</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>-46.58744000106517,168.80374900703666</t>
+        </is>
+      </c>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>-46.58705242591942,168.8030206690828</t>
+        </is>
+      </c>
+      <c r="J526" t="inlineStr">
+        <is>
+          <t>-46.58666380616117,168.8023049027835</t>
+        </is>
+      </c>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0548/nzd0548.xlsx
+++ b/data/nzd0548/nzd0548.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K526"/>
+  <dimension ref="A1:K527"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20938,6 +20938,45 @@
         <v>307.13</v>
       </c>
       <c r="K526" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:37+00:00</t>
+        </is>
+      </c>
+      <c r="B527" t="n">
+        <v>315.04</v>
+      </c>
+      <c r="C527" t="n">
+        <v>310.15</v>
+      </c>
+      <c r="D527" t="n">
+        <v>330.68</v>
+      </c>
+      <c r="E527" t="n">
+        <v>318.07</v>
+      </c>
+      <c r="F527" t="n">
+        <v>318.55</v>
+      </c>
+      <c r="G527" t="n">
+        <v>311.93</v>
+      </c>
+      <c r="H527" t="n">
+        <v>303.03</v>
+      </c>
+      <c r="I527" t="n">
+        <v>307.25</v>
+      </c>
+      <c r="J527" t="n">
+        <v>305.63</v>
+      </c>
+      <c r="K527" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -20954,7 +20993,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B552"/>
+  <dimension ref="A1:B553"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26477,6 +26516,16 @@
       </c>
       <c r="B552" t="n">
         <v>0.22</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B553" t="n">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -26645,28 +26694,28 @@
         <v>0.0565</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.372728107319064</v>
+        <v>-0.3710067773434486</v>
       </c>
       <c r="J2" t="n">
+        <v>526</v>
+      </c>
+      <c r="K2" t="n">
         <v>525</v>
       </c>
-      <c r="K2" t="n">
-        <v>524</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.1705975031905989</v>
+        <v>0.1697437859028733</v>
       </c>
       <c r="M2" t="n">
-        <v>4.39612536580026</v>
+        <v>4.394946511537898</v>
       </c>
       <c r="N2" t="n">
-        <v>38.45340407751156</v>
+        <v>38.41988958048172</v>
       </c>
       <c r="O2" t="n">
-        <v>6.201080879775038</v>
+        <v>6.198377979800983</v>
       </c>
       <c r="P2" t="n">
-        <v>320.5779432245232</v>
+        <v>320.559333504664</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26723,28 +26772,28 @@
         <v>0.0852</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1358761632004966</v>
+        <v>-0.1346630465270401</v>
       </c>
       <c r="J3" t="n">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="K3" t="n">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04273099687194082</v>
+        <v>0.04214000519405825</v>
       </c>
       <c r="M3" t="n">
-        <v>3.836475997960771</v>
+        <v>3.835374803605234</v>
       </c>
       <c r="N3" t="n">
-        <v>23.69990061534928</v>
+        <v>23.67476507788021</v>
       </c>
       <c r="O3" t="n">
-        <v>4.868254370444223</v>
+        <v>4.865672109573373</v>
       </c>
       <c r="P3" t="n">
-        <v>310.586167293959</v>
+        <v>310.5731119410556</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26801,28 +26850,28 @@
         <v>0.0808</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1858320702842171</v>
+        <v>-0.1836947914661673</v>
       </c>
       <c r="J4" t="n">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="K4" t="n">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="L4" t="n">
-        <v>0.06593474566238688</v>
+        <v>0.06464654214145116</v>
       </c>
       <c r="M4" t="n">
-        <v>4.206162606480442</v>
+        <v>4.208594970213194</v>
       </c>
       <c r="N4" t="n">
-        <v>28.03323485951348</v>
+        <v>28.04177483591251</v>
       </c>
       <c r="O4" t="n">
-        <v>5.294642089840774</v>
+        <v>5.295448501865778</v>
       </c>
       <c r="P4" t="n">
-        <v>329.9982464724793</v>
+        <v>329.9752454455929</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26879,28 +26928,28 @@
         <v>0.08119999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.21740014763641</v>
+        <v>-0.2156625039184558</v>
       </c>
       <c r="J5" t="n">
+        <v>526</v>
+      </c>
+      <c r="K5" t="n">
         <v>525</v>
       </c>
-      <c r="K5" t="n">
-        <v>524</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.08618245433033445</v>
+        <v>0.08514498535715853</v>
       </c>
       <c r="M5" t="n">
-        <v>4.227824931879467</v>
+        <v>4.228284872427158</v>
       </c>
       <c r="N5" t="n">
-        <v>28.7497469354121</v>
+        <v>28.73594053507673</v>
       </c>
       <c r="O5" t="n">
-        <v>5.361879048935373</v>
+        <v>5.360591435194136</v>
       </c>
       <c r="P5" t="n">
-        <v>319.3235042244328</v>
+        <v>319.3048056024991</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26957,28 +27006,28 @@
         <v>0.0701</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1467906726604769</v>
+        <v>-0.1445316161331207</v>
       </c>
       <c r="J6" t="n">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="K6" t="n">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04351307560977558</v>
+        <v>0.04230791829161196</v>
       </c>
       <c r="M6" t="n">
-        <v>4.271368660548273</v>
+        <v>4.273488016605119</v>
       </c>
       <c r="N6" t="n">
-        <v>27.33449847396746</v>
+        <v>27.35186021558636</v>
       </c>
       <c r="O6" t="n">
-        <v>5.22824047591228</v>
+        <v>5.229900593279605</v>
       </c>
       <c r="P6" t="n">
-        <v>316.4856031883386</v>
+        <v>316.4613541325652</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27035,28 +27084,28 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01579229346643831</v>
+        <v>0.01851810261675502</v>
       </c>
       <c r="J7" t="n">
+        <v>526</v>
+      </c>
+      <c r="K7" t="n">
         <v>525</v>
       </c>
-      <c r="K7" t="n">
-        <v>524</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.000194229463154505</v>
+        <v>0.0002678111251258608</v>
       </c>
       <c r="M7" t="n">
-        <v>6.77981908908506</v>
+        <v>6.778081338421091</v>
       </c>
       <c r="N7" t="n">
-        <v>73.69246558703229</v>
+        <v>73.65291076775907</v>
       </c>
       <c r="O7" t="n">
-        <v>8.584431582057853</v>
+        <v>8.582127403374939</v>
       </c>
       <c r="P7" t="n">
-        <v>304.2058531248477</v>
+        <v>304.1765366575851</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27113,28 +27162,28 @@
         <v>0.1109</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1066883189946918</v>
+        <v>0.1070984572421281</v>
       </c>
       <c r="J8" t="n">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="K8" t="n">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01204606187166768</v>
+        <v>0.01218803041149052</v>
       </c>
       <c r="M8" t="n">
-        <v>5.90220676309207</v>
+        <v>5.892543285878112</v>
       </c>
       <c r="N8" t="n">
-        <v>53.68131388316313</v>
+        <v>53.581156282697</v>
       </c>
       <c r="O8" t="n">
-        <v>7.326753297550227</v>
+        <v>7.319915046139333</v>
       </c>
       <c r="P8" t="n">
-        <v>299.0406722665123</v>
+        <v>299.036263939088</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27191,28 +27240,28 @@
         <v>0.095</v>
       </c>
       <c r="I9" t="n">
-        <v>0.08522235822697427</v>
+        <v>0.08847357818027543</v>
       </c>
       <c r="J9" t="n">
+        <v>526</v>
+      </c>
+      <c r="K9" t="n">
         <v>525</v>
       </c>
-      <c r="K9" t="n">
-        <v>524</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.003344263751722809</v>
+        <v>0.003614489831749057</v>
       </c>
       <c r="M9" t="n">
-        <v>9.385206541928822</v>
+        <v>9.381149128853812</v>
       </c>
       <c r="N9" t="n">
-        <v>123.2280511518891</v>
+        <v>123.1350682720595</v>
       </c>
       <c r="O9" t="n">
-        <v>11.10081308517034</v>
+        <v>11.09662418360014</v>
       </c>
       <c r="P9" t="n">
-        <v>296.2834492990166</v>
+        <v>296.2482995639927</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27269,28 +27318,28 @@
         <v>0.1205</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1548527306108798</v>
+        <v>0.1545965741615233</v>
       </c>
       <c r="J10" t="n">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="K10" t="n">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="L10" t="n">
-        <v>0.06319255210779418</v>
+        <v>0.06324461814840565</v>
       </c>
       <c r="M10" t="n">
-        <v>3.526967989189199</v>
+        <v>3.52164734625059</v>
       </c>
       <c r="N10" t="n">
-        <v>20.37000701013838</v>
+        <v>20.33216898668126</v>
       </c>
       <c r="O10" t="n">
-        <v>4.513314415165243</v>
+        <v>4.50912064450279</v>
       </c>
       <c r="P10" t="n">
-        <v>302.1166312071298</v>
+        <v>302.119387918762</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27328,7 +27377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K526"/>
+  <dimension ref="A1:K527"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57273,6 +57322,63 @@
         </is>
       </c>
     </row>
+    <row r="527">
+      <c r="A527" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:37+00:00</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>-46.59079222202782,168.80595088857768</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>-46.59017704371152,168.80605296690024</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>-46.5895312446579,168.80580141890863</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>-46.58893815225797,168.80544422822774</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>-46.58840549876259,168.804939823942</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>-46.587911838363254,168.80435087259903</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>-46.58742981235715,168.8037633556011</t>
+        </is>
+      </c>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>-46.587041267113065,168.8030348372306</t>
+        </is>
+      </c>
+      <c r="J527" t="inlineStr">
+        <is>
+          <t>-46.586653327210975,168.80231720638884</t>
+        </is>
+      </c>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
